--- a/tests/workbooktests/workbooks/test_gaussian1dmodel.xlsx
+++ b/tests/workbooktests/workbooks/test_gaussian1dmodel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2FC726-D8B8-4AD7-8809-B6520A5E18F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F786642-E4F7-4FE1-81CD-045F3DFD31B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{096EF196-26B4-4940-94D5-2518E57D2FCB}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{096EF196-26B4-4940-94D5-2518E57D2FCB}"/>
   </bookViews>
   <sheets>
     <sheet name="GSR Model and Engine" sheetId="1" r:id="rId1"/>
@@ -843,35 +843,35 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" cm="1">
-        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>46174</v>
+      <c r="B2" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="str" cm="1">
-        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03,"Act/365")</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
+      <c r="B4" t="e" cm="1">
+        <f t="array" aca="1" ref="B4" ca="1">_xll.qlFlatForward(B2,0.03,"Act/365")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1">
-        <f>B2+365</f>
-        <v>46539</v>
-      </c>
-      <c r="C8" s="1">
-        <f>B8+365</f>
-        <v>46904</v>
-      </c>
-      <c r="D8" s="1">
-        <f>C8+365</f>
-        <v>47269</v>
+      <c r="B8" s="1" t="e">
+        <f ca="1">B2+365</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="1" t="e">
+        <f ca="1">B8+365</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D8" s="1" t="e">
+        <f ca="1">C8+365</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="1"/>
     </row>
@@ -921,36 +921,36 @@
       <c r="A13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B13" t="str" cm="1">
-        <f t="array" ref="B13">_xll.qlGsr(B4,B8:D8,B9:E9,B10:E10,B11)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R13C2Gsr,A</v>
+      <c r="B13" t="e" cm="1">
+        <f t="array" aca="1" ref="B13" ca="1">_xll.qlGsr(B4,B8:D8,B9:E9,B10:E10,B11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B15" t="str" cm="1">
-        <f t="array" ref="B15">_xll.qlGaussian1dSwaptionEngine(B13)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R15C2Gaussian1dSwaptionEngine,A</v>
+      <c r="B15" t="e" cm="1">
+        <f t="array" aca="1" ref="B15" ca="1">_xll.qlGaussian1dSwaptionEngine(B13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="4" t="str" cm="1">
-        <f t="array" ref="B17">_xll.qlFlatForward(B2,0.03)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R17C2YieldTermStructureHandle,A</v>
+      <c r="B17" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlFlatForward(B2,0.03)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="4" t="str" cm="1">
-        <f t="array" ref="B18">_xll.qlEuribor("6M",B17)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
+      <c r="B18" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B18" ca="1">_xll.qlEuribor("6M",B17)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -976,18 +976,18 @@
       <c r="A22" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="3" cm="1">
-        <f t="array" ref="B22">_xll.qlCalendarAdvance2("Target",$B$2,B20,"ModifiedFollowing")</f>
-        <v>46905</v>
+      <c r="B22" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B22" ca="1">_xll.qlCalendarAdvance2("Target",$B$2,B20,"ModifiedFollowing")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="3" cm="1">
-        <f t="array" ref="B23">_xll.qlCalendarAdvance2("Target",$B$2,B21,"ModifiedFollowing")</f>
-        <v>48001</v>
+      <c r="B23" s="3" t="e" cm="1">
+        <f t="array" aca="1" ref="B23" ca="1">_xll.qlCalendarAdvance2("Target",$B$2,B21,"ModifiedFollowing")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -1002,27 +1002,27 @@
       <c r="A25" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="4" t="str" cm="1">
-        <f t="array" ref="B25">_xll.qlMakeSchedule(B22,B23,"1y",,"Target","ModifiedFollowing",,"Backward")</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R25C2Schedule,A</v>
+      <c r="B25" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B25" ca="1">_xll.qlMakeSchedule(B22,B23,"1y",,"Target","ModifiedFollowing",,"Backward")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="4" t="str" cm="1">
-        <f t="array" ref="B26">_xll.qlMakeSchedule(B22,B23,"6m",,"Target","ModifiedFollowing",,"Backward")</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R26C2Schedule,A</v>
+      <c r="B26" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B26" ca="1">_xll.qlMakeSchedule(B22,B23,"6m",,"Target","ModifiedFollowing",,"Backward")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="4" t="str" cm="1">
-        <f t="array" ref="B27">_xll.qlVanillaSwap("Payer",10000,B25,B24,"30/360",B26,B18,0,"Act/360")</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R27C2VanillaSwap,A</v>
+      <c r="B27" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B27" ca="1">_xll.qlVanillaSwap("Payer",10000,B25,B24,"30/360",B26,B18,0,"Act/360")</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1032,30 +1032,22 @@
       <c r="A29" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="3">
-        <f t="array" ref="B29:B33">_xll.qlScheduleDates(B25) - 2</f>
-        <v>46903</v>
+      <c r="B29" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B29" ca="1">_xll.qlScheduleDates(B25) - 2</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B30" s="3">
-        <v>46904</v>
-      </c>
+      <c r="B30" s="3"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B31" s="3">
-        <v>47271</v>
-      </c>
+      <c r="B31" s="3"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B32" s="3">
-        <v>47635</v>
-      </c>
+      <c r="B32" s="3"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="6">
-        <v>47999</v>
-      </c>
+      <c r="B33" s="6"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B34" s="4"/>
@@ -1064,18 +1056,18 @@
       <c r="A35" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="4" t="str" cm="1">
-        <f t="array" ref="B35">_xll.qlEuropeanExercise(B29)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R35C2EuropeanExercise,A</v>
+      <c r="B35" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B35" ca="1">_xll.qlEuropeanExercise(B29)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="4" t="str" cm="1">
-        <f t="array" ref="B36">_xll.qlBermudanExercise(B29:B32)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R36C2BermudanExercise,A</v>
+      <c r="B36" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B36" ca="1">_xll.qlBermudanExercise(B29:B32)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1100,36 +1092,36 @@
       <c r="A41" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="4" t="str" cm="1">
-        <f t="array" ref="B41">_xll.qlSwaption(B27,B35)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R41C2Swaption,A</v>
+      <c r="B41" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B41" ca="1">_xll.qlSwaption(B27,B35)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>27</v>
       </c>
-      <c r="B42" s="4" t="str" cm="1">
-        <f t="array" ref="B42">_xll.qlSwaption(B27,B36)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R42C2Swaption,A</v>
+      <c r="B42" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B42" ca="1">_xll.qlSwaption(B27,B36)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>28</v>
       </c>
-      <c r="B44" cm="1">
-        <f t="array" ref="B44">_xll.qlInstrumentNPV(B41,_xll.qlInstrumentSetPricingEngine(B41,B15))</f>
-        <v>126.78027860072081</v>
+      <c r="B44" t="e" cm="1">
+        <f t="array" aca="1" ref="B44" ca="1">_xll.qlInstrumentNPV(B41,_xll.qlInstrumentSetPricingEngine(B41,B15))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>28</v>
       </c>
-      <c r="B45" cm="1">
-        <f t="array" ref="B45">_xll.qlInstrumentNPV(B42,_xll.qlInstrumentSetPricingEngine(B42,B15))</f>
-        <v>143.1754771873166</v>
+      <c r="B45" t="e" cm="1">
+        <f t="array" aca="1" ref="B45" ca="1">_xll.qlInstrumentNPV(B42,_xll.qlInstrumentSetPricingEngine(B42,B15))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1201,21 +1193,21 @@
       <c r="A52" t="s">
         <v>35</v>
       </c>
-      <c r="B52" s="4" t="str">
-        <f>$B$18</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
-      </c>
-      <c r="C52" s="4" t="str">
-        <f>$B$18</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
-      </c>
-      <c r="D52" s="4" t="str">
-        <f>$B$18</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
-      </c>
-      <c r="E52" s="4" t="str">
-        <f>$B$18</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
+      <c r="B52" s="4" t="e">
+        <f ca="1">$B$18</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C52" s="4" t="e">
+        <f ca="1">$B$18</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D52" s="4" t="e">
+        <f ca="1">$B$18</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E52" s="4" t="e">
+        <f ca="1">$B$18</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1273,21 +1265,21 @@
       <c r="A56" t="s">
         <v>42</v>
       </c>
-      <c r="B56" s="4" t="str">
-        <f>$B$4</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="C56" s="4" t="str">
-        <f>$B$4</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="D56" s="4" t="str">
-        <f>$B$4</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
-      </c>
-      <c r="E56" s="4" t="str">
-        <f>$B$4</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
+      <c r="B56" s="4" t="e">
+        <f ca="1">$B$4</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C56" s="4" t="e">
+        <f ca="1">$B$4</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D56" s="4" t="e">
+        <f ca="1">$B$4</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E56" s="4" t="e">
+        <f ca="1">$B$4</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1413,48 +1405,48 @@
       <c r="A65" t="s">
         <v>29</v>
       </c>
-      <c r="B65" s="4" t="str" cm="1">
-        <f t="array" ref="B65">_xll.qlSwaptionHelper(B49,B50,B51,B52,B53,B54,B55,B56,B57,B58,B59,B60,B61,B62)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C2SwaptionHelper,A</v>
-      </c>
-      <c r="C65" s="4" t="str" cm="1">
-        <f t="array" ref="C65">_xll.qlSwaptionHelper(C49,C50,C51,C52,C53,C54,C55,C56,C57,C58,C59,C60,C61,C62)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C3SwaptionHelper,A</v>
-      </c>
-      <c r="D65" s="4" t="str" cm="1">
-        <f t="array" ref="D65">_xll.qlSwaptionHelper(D49,D50,D51,D52,D53,D54,D55,D56,D57,D58,D59,D60,D61,D62)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C4SwaptionHelper,A</v>
-      </c>
-      <c r="E65" s="4" t="str" cm="1">
-        <f t="array" ref="E65">_xll.qlSwaptionHelper(E49,E50,E51,E52,E53,E54,E55,E56,E57,E58,E59,E60,E61,E62)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C5SwaptionHelper,A</v>
+      <c r="B65" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B65" ca="1">_xll.qlSwaptionHelper(B49,B50,B51,B52,B53,B54,B55,B56,B57,B58,B59,B60,B61,B62)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C65" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="C65" ca="1">_xll.qlSwaptionHelper(C49,C50,C51,C52,C53,C54,C55,C56,C57,C58,C59,C60,C61,C62)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D65" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="D65" ca="1">_xll.qlSwaptionHelper(D49,D50,D51,D52,D53,D54,D55,D56,D57,D58,D59,D60,D61,D62)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E65" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="E65" ca="1">_xll.qlSwaptionHelper(E49,E50,E51,E52,E53,E54,E55,E56,E57,E58,E59,E60,E61,E62)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B66" t="b" cm="1">
-        <f t="array" ref="B66">_xll.qlBlackCalibrationHelperSetPricingEngine(B65,$B$15)</f>
-        <v>1</v>
-      </c>
-      <c r="C66" t="b" cm="1">
-        <f t="array" ref="C66">_xll.qlBlackCalibrationHelperSetPricingEngine(C65,$B$15)</f>
-        <v>1</v>
-      </c>
-      <c r="D66" t="b" cm="1">
-        <f t="array" ref="D66">_xll.qlBlackCalibrationHelperSetPricingEngine(D65,$B$15)</f>
-        <v>1</v>
-      </c>
-      <c r="E66" t="b" cm="1">
-        <f t="array" ref="E66">_xll.qlBlackCalibrationHelperSetPricingEngine(E65,$B$15)</f>
-        <v>1</v>
+      <c r="B66" t="e" cm="1">
+        <f t="array" aca="1" ref="B66" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B65,$B$15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C66" t="e" cm="1">
+        <f t="array" aca="1" ref="C66" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(C65,$B$15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D66" t="e" cm="1">
+        <f t="array" aca="1" ref="D66" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(D65,$B$15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E66" t="e" cm="1">
+        <f t="array" aca="1" ref="E66" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(E65,$B$15)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>55</v>
       </c>
-      <c r="B68" t="str" cm="1">
-        <f t="array" ref="B68">_xll.qlLevenbergMarquardt(,,,,B66:E66)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R68C2LevenbergMarquardt,A</v>
+      <c r="B68" t="e" cm="1">
+        <f t="array" aca="1" ref="B68" ca="1">_xll.qlLevenbergMarquardt(,,,,B66:E66)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -1501,54 +1493,36 @@
       <c r="A75" t="s">
         <v>61</v>
       </c>
-      <c r="B75" t="str" cm="1">
-        <f t="array" ref="B75">_xll.qlEndCriteria(B70,B71,B72,B73,B74,B66:E66)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]GSR Model and Engine!R75C2EndCriteria,A</v>
+      <c r="B75" t="e" cm="1">
+        <f t="array" aca="1" ref="B75" ca="1">_xll.qlEndCriteria(B70,B71,B72,B73,B74,B66:E66)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>62</v>
       </c>
-      <c r="B77" t="b" cm="1">
-        <f t="array" ref="B77">_xll.qlGsrCalibrateVolatilitiesIterative(B13,B65:E65,B68,B75,,,B66:E66)</f>
-        <v>1</v>
+      <c r="B77" t="e" cm="1">
+        <f t="array" aca="1" ref="B77" ca="1">_xll.qlGsrCalibrateVolatilitiesIterative(B13,B65:E65,B68,B75,,,B66:E66)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B79" cm="1">
-        <f t="array" ref="B79:E79">TRANSPOSE(_xll.qlGsrVolatility(B13,B77))</f>
-        <v>6.9631874311834709E-3</v>
-      </c>
-      <c r="C79">
-        <v>6.9598377904623336E-3</v>
-      </c>
-      <c r="D79">
-        <v>6.9692472977811214E-3</v>
-      </c>
-      <c r="E79">
-        <v>6.9991762124002365E-3</v>
+      <c r="B79" t="e" cm="1">
+        <f t="array" aca="1" ref="B79" ca="1">TRANSPOSE(_xll.qlGsrVolatility(B13,B77))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B80" cm="1">
-        <f t="array" ref="B80:E80">TRANSPOSE(_xll.qlGsrReversion(B13,B77))</f>
-        <v>0.01</v>
-      </c>
-      <c r="C80">
-        <v>0.01</v>
-      </c>
-      <c r="D80">
-        <v>0.01</v>
-      </c>
-      <c r="E80">
-        <v>0.01</v>
+      <c r="B80" t="e" cm="1">
+        <f t="array" aca="1" ref="B80" ca="1">TRANSPOSE(_xll.qlGsrReversion(B13,B77))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1588,9 +1562,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" cm="1">
-        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>46174</v>
+      <c r="B2" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
@@ -1680,33 +1654,33 @@
       <c r="J5" s="2">
         <v>6.7945145206867591E-3</v>
       </c>
-      <c r="K5" s="1" cm="1">
-        <f t="array" ref="K5">_xll.qlCalendarAdvance2($B$4,$B$2,D5)</f>
-        <v>46905</v>
+      <c r="K5" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="K5" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D5)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="L5" s="13"/>
       <c r="O5" s="12">
         <v>1</v>
       </c>
-      <c r="P5" s="1" cm="1">
-        <f t="array" ref="P5">INDEX(_xll.qlScheduleDates($B$20),O5)</f>
-        <v>46541</v>
-      </c>
-      <c r="Q5" s="1" cm="1">
-        <f t="array" ref="Q5">_xll.qlCalendarAdvance2($B$4,P5,"-2d")</f>
-        <v>46539</v>
+      <c r="P5" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="P5" ca="1">INDEX(_xll.qlScheduleDates($B$20),O5)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q5" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="Q5" ca="1">_xll.qlCalendarAdvance2($B$4,P5,"-2d")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="R5" s="14" t="str">
         <f>(10-O5)&amp;"y"</f>
         <v>9y</v>
       </c>
-      <c r="S5" s="15" cm="1">
-        <f t="array" ref="S5">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q5,R5,$B$23)</f>
-        <v>6.8416161029777513E-3</v>
-      </c>
-      <c r="T5" s="4" t="str" cm="1">
-        <f t="array" ref="T5">_xll.qlSwaptionHelper(Q5,R5,S5,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R5C20SwaptionHelper,A</v>
+      <c r="S5" s="15" t="e" cm="1">
+        <f t="array" aca="1" ref="S5" ca="1">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q5,R5,$B$23)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T5" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="T5" ca="1">_xll.qlSwaptionHelper(Q5,R5,S5,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="U5" s="13">
         <v>7.0000000000000001E-3</v>
@@ -1715,22 +1689,22 @@
         <f>$B$39</f>
         <v>0.03</v>
       </c>
-      <c r="W5" t="b" cm="1">
-        <f t="array" ref="W5">_xll.qlBlackCalibrationHelperSetPricingEngine(T5,$B$41)</f>
-        <v>1</v>
-      </c>
-      <c r="X5" s="2" cm="1">
-        <f t="array" ref="X5:X10">_xll.qlGsrVolatility(B40,B52)</f>
-        <v>7.6211372531143793E-3</v>
+      <c r="W5" t="e" cm="1">
+        <f t="array" aca="1" ref="W5" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(T5,$B$41)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X5" s="2" t="e" cm="1">
+        <f t="array" aca="1" ref="X5" ca="1">_xll.qlGsrVolatility(B40,B52)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="4" t="str" cm="1">
-        <f t="array" ref="B6">_xll.qlFlatForward($B$2,0.03,"Act/365")</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R6C2YieldTermStructureHandle,A</v>
+      <c r="B6" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B6" ca="1">_xll.qlFlatForward($B$2,0.03,"Act/365")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>68</v>
@@ -1753,32 +1727,32 @@
       <c r="J6" s="2">
         <v>6.7609933594352887E-3</v>
       </c>
-      <c r="K6" s="1" cm="1">
-        <f t="array" ref="K6">_xll.qlCalendarAdvance2($B$4,$B$2,D6)</f>
-        <v>47270</v>
+      <c r="K6" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="K6" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D6)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="O6" s="12">
         <v>3</v>
       </c>
-      <c r="P6" s="1" cm="1">
-        <f t="array" ref="P6">INDEX(_xll.qlScheduleDates($B$20),O6)</f>
-        <v>47273</v>
-      </c>
-      <c r="Q6" s="1" cm="1">
-        <f t="array" ref="Q6">_xll.qlCalendarAdvance2($B$4,P6,"-2d")</f>
-        <v>47269</v>
+      <c r="P6" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="P6" ca="1">INDEX(_xll.qlScheduleDates($B$20),O6)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q6" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="Q6" ca="1">_xll.qlCalendarAdvance2($B$4,P6,"-2d")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="R6" s="14" t="str">
         <f t="shared" ref="R6:R9" si="0">(10-O6)&amp;"y"</f>
         <v>7y</v>
       </c>
-      <c r="S6" s="15" cm="1">
-        <f t="array" ref="S6">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q6,R6,$B$23)</f>
-        <v>6.8685932674608981E-3</v>
-      </c>
-      <c r="T6" s="4" t="str" cm="1">
-        <f t="array" ref="T6">_xll.qlSwaptionHelper(Q6,R6,S6,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R6C20SwaptionHelper,A</v>
+      <c r="S6" s="15" t="e" cm="1">
+        <f t="array" aca="1" ref="S6" ca="1">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q6,R6,$B$23)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T6" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="T6" ca="1">_xll.qlSwaptionHelper(Q6,R6,S6,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="U6" s="13">
         <v>7.0000000000000001E-3</v>
@@ -1787,21 +1761,19 @@
         <f t="shared" ref="V6:V10" si="1">$B$39</f>
         <v>0.03</v>
       </c>
-      <c r="W6" t="b" cm="1">
-        <f t="array" ref="W6">_xll.qlBlackCalibrationHelperSetPricingEngine(T6,$B$41)</f>
-        <v>1</v>
-      </c>
-      <c r="X6" s="2">
-        <v>7.7086247092700601E-3</v>
-      </c>
+      <c r="W6" t="e" cm="1">
+        <f t="array" aca="1" ref="W6" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(T6,$B$41)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X6" s="2"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="4" t="str" cm="1">
-        <f t="array" ref="B7">_xll.qlFlatForward($B$2,0.02,"Act/365")</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R7C2YieldTermStructureHandle,A</v>
+      <c r="B7" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B7" ca="1">_xll.qlFlatForward($B$2,0.02,"Act/365")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>69</v>
@@ -1824,32 +1796,32 @@
       <c r="J7" s="2">
         <v>6.667429100858718E-3</v>
       </c>
-      <c r="K7" s="1" cm="1">
-        <f t="array" ref="K7">_xll.qlCalendarAdvance2($B$4,$B$2,D7)</f>
-        <v>47637</v>
+      <c r="K7" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="K7" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D7)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="O7" s="12">
         <v>5</v>
       </c>
-      <c r="P7" s="1" cm="1">
-        <f t="array" ref="P7">INDEX(_xll.qlScheduleDates($B$20),O7)</f>
-        <v>48002</v>
-      </c>
-      <c r="Q7" s="1" cm="1">
-        <f t="array" ref="Q7">_xll.qlCalendarAdvance2($B$4,P7,"-2d")</f>
-        <v>47998</v>
+      <c r="P7" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="P7" ca="1">INDEX(_xll.qlScheduleDates($B$20),O7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q7" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="Q7" ca="1">_xll.qlCalendarAdvance2($B$4,P7,"-2d")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="R7" s="14" t="str">
         <f t="shared" si="0"/>
         <v>5y</v>
       </c>
-      <c r="S7" s="15" cm="1">
-        <f t="array" ref="S7">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q7,R7,$B$23)</f>
-        <v>6.8308101938307384E-3</v>
-      </c>
-      <c r="T7" s="4" t="str" cm="1">
-        <f t="array" ref="T7">_xll.qlSwaptionHelper(Q7,R7,S7,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R7C20SwaptionHelper,A</v>
+      <c r="S7" s="15" t="e" cm="1">
+        <f t="array" aca="1" ref="S7" ca="1">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q7,R7,$B$23)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T7" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="T7" ca="1">_xll.qlSwaptionHelper(Q7,R7,S7,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="U7" s="13">
         <v>7.0000000000000001E-3</v>
@@ -1858,13 +1830,11 @@
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="W7" t="b" cm="1">
-        <f t="array" ref="W7">_xll.qlBlackCalibrationHelperSetPricingEngine(T7,$B$41)</f>
-        <v>1</v>
-      </c>
-      <c r="X7" s="2">
-        <v>7.5952162222992737E-3</v>
-      </c>
+      <c r="W7" t="e" cm="1">
+        <f t="array" aca="1" ref="W7" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(T7,$B$41)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X7" s="2"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="D8" s="12" t="s">
@@ -1888,32 +1858,32 @@
       <c r="J8" s="2">
         <v>6.5734245883187388E-3</v>
       </c>
-      <c r="K8" s="1" cm="1">
-        <f t="array" ref="K8">_xll.qlCalendarAdvance2($B$4,$B$2,D8)</f>
-        <v>48001</v>
+      <c r="K8" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="K8" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D8)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="O8" s="12">
         <v>7</v>
       </c>
-      <c r="P8" s="1" cm="1">
-        <f t="array" ref="P8">INDEX(_xll.qlScheduleDates($B$20),O8)</f>
-        <v>48733</v>
-      </c>
-      <c r="Q8" s="1" cm="1">
-        <f t="array" ref="Q8">_xll.qlCalendarAdvance2($B$4,P8,"-2d")</f>
-        <v>48731</v>
+      <c r="P8" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="P8" ca="1">INDEX(_xll.qlScheduleDates($B$20),O8)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q8" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="Q8" ca="1">_xll.qlCalendarAdvance2($B$4,P8,"-2d")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="R8" s="14" t="str">
         <f t="shared" si="0"/>
         <v>3y</v>
       </c>
-      <c r="S8" s="15" cm="1">
-        <f t="array" ref="S8">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q8,R8,$B$23)</f>
-        <v>6.7802047066821882E-3</v>
-      </c>
-      <c r="T8" s="4" t="str" cm="1">
-        <f t="array" ref="T8">_xll.qlSwaptionHelper(Q8,R8,S8,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R8C20SwaptionHelper,A</v>
+      <c r="S8" s="15" t="e" cm="1">
+        <f t="array" aca="1" ref="S8" ca="1">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q8,R8,$B$23)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T8" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="T8" ca="1">_xll.qlSwaptionHelper(Q8,R8,S8,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="U8" s="13">
         <v>7.0000000000000001E-3</v>
@@ -1922,21 +1892,19 @@
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="W8" t="b" cm="1">
-        <f t="array" ref="W8">_xll.qlBlackCalibrationHelperSetPricingEngine(T8,$B$41)</f>
-        <v>1</v>
-      </c>
-      <c r="X8" s="2">
-        <v>7.4940275000552952E-3</v>
-      </c>
+      <c r="W8" t="e" cm="1">
+        <f t="array" aca="1" ref="W8" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(T8,$B$41)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X8" s="2"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="4" t="str" cm="1">
-        <f t="array" ref="B9">_xll.qlSwaptionVolatilityMatrix(B2,K5:K13,E4:J4,E5:J13,"act/365",,"Normal")</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R9C2SwaptionVolatilityStructureHandle,A</v>
+      <c r="B9" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B9" ca="1">_xll.qlSwaptionVolatilityMatrix(B2,K5:K13,E4:J4,E5:J13,"act/365",,"Normal")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>70</v>
@@ -1959,32 +1927,32 @@
       <c r="J9" s="2">
         <v>6.4205016338086587E-3</v>
       </c>
-      <c r="K9" s="1" cm="1">
-        <f t="array" ref="K9">_xll.qlCalendarAdvance2($B$4,$B$2,D9)</f>
-        <v>48366</v>
+      <c r="K9" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="K9" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D9)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="O9" s="12">
         <v>9</v>
       </c>
-      <c r="P9" s="1" cm="1">
-        <f t="array" ref="P9">INDEX(_xll.qlScheduleDates($B$20),O9)</f>
-        <v>49464</v>
-      </c>
-      <c r="Q9" s="1" cm="1">
-        <f t="array" ref="Q9">_xll.qlCalendarAdvance2($B$4,P9,"-2d")</f>
-        <v>49460</v>
+      <c r="P9" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="P9" ca="1">INDEX(_xll.qlScheduleDates($B$20),O9)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q9" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="Q9" ca="1">_xll.qlCalendarAdvance2($B$4,P9,"-2d")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="R9" s="14" t="str">
         <f t="shared" si="0"/>
         <v>1y</v>
       </c>
-      <c r="S9" s="15" cm="1">
-        <f t="array" ref="S9">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q9,R9,$B$23)</f>
-        <v>6.7856340498962438E-3</v>
-      </c>
-      <c r="T9" s="4" t="str" cm="1">
-        <f t="array" ref="T9">_xll.qlSwaptionHelper(Q9,R9,S9,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R9C20SwaptionHelper,A</v>
+      <c r="S9" s="15" t="e" cm="1">
+        <f t="array" aca="1" ref="S9" ca="1">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q9,R9,$B$23)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T9" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="T9" ca="1">_xll.qlSwaptionHelper(Q9,R9,S9,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="U9" s="13">
         <v>7.0000000000000001E-3</v>
@@ -1993,13 +1961,11 @@
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="W9" t="b" cm="1">
-        <f t="array" ref="W9">_xll.qlBlackCalibrationHelperSetPricingEngine(T9,$B$41)</f>
-        <v>1</v>
-      </c>
-      <c r="X9" s="2">
-        <v>7.5255128544283187E-3</v>
-      </c>
+      <c r="W9" t="e" cm="1">
+        <f t="array" aca="1" ref="W9" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(T9,$B$41)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X9" s="2"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="D10" s="12" t="s">
@@ -2023,9 +1989,9 @@
       <c r="J10" s="2">
         <v>6.2645776071992877E-3</v>
       </c>
-      <c r="K10" s="1" cm="1">
-        <f t="array" ref="K10">_xll.qlCalendarAdvance2($B$4,$B$2,D10)</f>
-        <v>48731</v>
+      <c r="K10" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="K10" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D10)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="U10" s="13">
         <v>7.0000000000000001E-3</v>
@@ -2034,17 +2000,15 @@
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="X10" s="2">
-        <v>7.0000000000000001E-3</v>
-      </c>
+      <c r="X10" s="2"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="str" cm="1">
-        <f t="array" ref="B11">_xll.qlEuribor("6m",B6)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R11C2Euribor,A</v>
+      <c r="B11" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlEuribor("6m",B6)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>72</v>
@@ -2067,9 +2031,9 @@
       <c r="J11" s="2">
         <v>6.0960353967729093E-3</v>
       </c>
-      <c r="K11" s="1" cm="1">
-        <f t="array" ref="K11">_xll.qlCalendarAdvance2($B$4,$B$2,D11)</f>
-        <v>49096</v>
+      <c r="K11" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="K11" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
@@ -2094,9 +2058,9 @@
       <c r="J12" s="2">
         <v>5.9343809605290482E-3</v>
       </c>
-      <c r="K12" s="1" cm="1">
-        <f t="array" ref="K12">_xll.qlCalendarAdvance2($B$4,$B$2,D12)</f>
-        <v>49461</v>
+      <c r="K12" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="K12" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D12)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
@@ -2127,9 +2091,9 @@
       <c r="J13" s="2">
         <v>5.7827242854212382E-3</v>
       </c>
-      <c r="K13" s="1" cm="1">
-        <f t="array" ref="K13">_xll.qlCalendarAdvance2($B$4,$B$2,D13)</f>
-        <v>49828</v>
+      <c r="K13" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="K13" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D13)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -2152,9 +2116,9 @@
       <c r="A17" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="1" cm="1">
-        <f t="array" ref="B17">_xll.qlCalendarAdvance2($B$4,_xll.qlCalendarAdvance2($B$4,$B$2,$B$13),$B$15)</f>
-        <v>46541</v>
+      <c r="B17" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlCalendarAdvance2($B$4,_xll.qlCalendarAdvance2($B$4,$B$2,$B$13),$B$15)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="L17" s="1"/>
     </row>
@@ -2162,9 +2126,9 @@
       <c r="A18" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="1" cm="1">
-        <f t="array" ref="B18">_xll.qlCalendarAdvance2($B$4,$B$17,$B$14)</f>
-        <v>50194</v>
+      <c r="B18" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B18" ca="1">_xll.qlCalendarAdvance2($B$4,$B$17,$B$14)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="L18" s="1"/>
     </row>
@@ -2175,9 +2139,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="4" t="str" cm="1">
-        <f t="array" ref="B20">_xll.qlMakeSchedule($B$17,$B$18,"1y",,$B$4,"Following",,"Backward")</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R20C2Schedule,A</v>
+      <c r="B20" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B20" ca="1">_xll.qlMakeSchedule($B$17,$B$18,"1y",,$B$4,"Following",,"Backward")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="L20" s="1"/>
     </row>
@@ -2185,9 +2149,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="4" t="str" cm="1">
-        <f t="array" ref="B21">_xll.qlMakeSchedule($B$17,$B$18,"3m",,$B$4,"Following",,"Backward")</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R21C2Schedule,A</v>
+      <c r="B21" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B21" ca="1">_xll.qlMakeSchedule($B$17,$B$18,"3m",,$B$4,"Following",,"Backward")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="L21" s="1"/>
     </row>
@@ -2219,9 +2183,9 @@
       <c r="A26" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="4" t="str" cm="1">
-        <f t="array" ref="B26">_xll.qlVanillaSwap("Payer",10000,$B$20,$B$23,$B$24,$B$21,$B$11,0,"act/360")</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R26C2VanillaSwap,A</v>
+      <c r="B26" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B26" ca="1">_xll.qlVanillaSwap("Payer",10000,$B$20,$B$23,$B$24,$B$21,$B$11,0,"act/360")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="L26" s="1"/>
     </row>
@@ -2232,63 +2196,63 @@
       <c r="A28" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="4" t="str" cm="1">
-        <f t="array" ref="B28">_xll.qlBermudanExercise(Q5:Q9)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R28C2BermudanExercise,A</v>
+      <c r="B28" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B28" ca="1">_xll.qlBermudanExercise(Q5:Q9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="4" t="str" cm="1">
-        <f t="array" ref="B30">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q5))</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R30C2Swaption,A</v>
+      <c r="B30" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B30" ca="1">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q5))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="4" t="str" cm="1">
-        <f t="array" ref="B31">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q6))</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R31C2Swaption,A</v>
+      <c r="B31" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B31" ca="1">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q6))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="4" t="str" cm="1">
-        <f t="array" ref="B32">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q7))</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R32C2Swaption,A</v>
+      <c r="B32" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B32" ca="1">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q7))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="4" t="str" cm="1">
-        <f t="array" ref="B33">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q8))</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R33C2Swaption,A</v>
+      <c r="B33" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B33" ca="1">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q8))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="4" t="str" cm="1">
-        <f t="array" ref="B34">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q9))</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R34C2Swaption,A</v>
+      <c r="B34" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B34" ca="1">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q9))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="4" t="str" cm="1">
-        <f t="array" ref="B36">_xll.qlSwaption(B26,B28)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R36C2Swaption,A</v>
+      <c r="B36" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B36" ca="1">_xll.qlSwaption(B26,B28)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -2309,27 +2273,27 @@
       <c r="A40" t="s">
         <v>96</v>
       </c>
-      <c r="B40" s="4" t="str" cm="1">
-        <f t="array" ref="B40">_xll.qlGsr(B7,Q5:Q9,U5:U10,V5:V10)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R40C2Gsr,A</v>
+      <c r="B40" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B40" ca="1">_xll.qlGsr(B7,Q5:Q9,U5:U10,V5:V10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="4" t="str" cm="1">
-        <f t="array" ref="B41">_xll.qlGaussian1dSwaptionEngine(B40)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R41C2Gaussian1dSwaptionEngine,A</v>
+      <c r="B41" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B41" ca="1">_xll.qlGaussian1dSwaptionEngine(B40)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="4" t="str" cm="1">
-        <f t="array" ref="B43">_xll.qlLevenbergMarquardt(,,,,T5:T9)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R43C2LevenbergMarquardt,O</v>
+      <c r="B43" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B43" ca="1">_xll.qlLevenbergMarquardt(,,,,T5:T9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -2376,18 +2340,18 @@
       <c r="A50" t="s">
         <v>100</v>
       </c>
-      <c r="B50" s="4" t="str" cm="1">
-        <f t="array" ref="B50">_xll.qlEndCriteria(B45,B46,B47,B48,B49,T5:T9)</f>
-        <v>⚡[test_gaussian1dmodel.xlsx]Bermudan Swaption!R50C2EndCriteria,P</v>
+      <c r="B50" s="4" t="e" cm="1">
+        <f t="array" aca="1" ref="B50" ca="1">_xll.qlEndCriteria(B45,B46,B47,B48,B49,T5:T9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>105</v>
       </c>
-      <c r="B52" t="b" cm="1">
-        <f t="array" ref="B52">_xll.qlGsrCalibrateVolatilitiesIterative(B40,T5:T9,B43,B50,,,W5:W9)</f>
-        <v>1</v>
+      <c r="B52" t="e" cm="1">
+        <f t="array" aca="1" ref="B52" ca="1">_xll.qlGsrCalibrateVolatilitiesIterative(B40,T5:T9,B43,B50,,,W5:W9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -2399,63 +2363,63 @@
       <c r="A55" t="s">
         <v>90</v>
       </c>
-      <c r="B55" s="17" cm="1">
-        <f t="array" ref="B55">_xll.qlInstrumentNPV(B30,_xll.qlInstrumentSetPricingEngine(B30,$B$41,$B$52))</f>
-        <v>21.703395415539141</v>
+      <c r="B55" s="17" t="e" cm="1">
+        <f t="array" aca="1" ref="B55" ca="1">_xll.qlInstrumentNPV(B30,_xll.qlInstrumentSetPricingEngine(B30,$B$41,$B$52))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="17" cm="1">
-        <f t="array" ref="B56">_xll.qlInstrumentNPV(B31,_xll.qlInstrumentSetPricingEngine(B31,$B$41,$B$52))</f>
-        <v>96.520281949812968</v>
+      <c r="B56" s="17" t="e" cm="1">
+        <f t="array" aca="1" ref="B56" ca="1">_xll.qlInstrumentNPV(B31,_xll.qlInstrumentSetPricingEngine(B31,$B$41,$B$52))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>92</v>
       </c>
-      <c r="B57" s="17" cm="1">
-        <f t="array" ref="B57">_xll.qlInstrumentNPV(B32,_xll.qlInstrumentSetPricingEngine(B32,$B$41,$B$52))</f>
-        <v>123.61092110727894</v>
+      <c r="B57" s="17" t="e" cm="1">
+        <f t="array" aca="1" ref="B57" ca="1">_xll.qlInstrumentNPV(B32,_xll.qlInstrumentSetPricingEngine(B32,$B$41,$B$52))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>93</v>
       </c>
-      <c r="B58" s="17" cm="1">
-        <f t="array" ref="B58">_xll.qlInstrumentNPV(B33,_xll.qlInstrumentSetPricingEngine(B33,$B$41,$B$52))</f>
-        <v>110.3399969979758</v>
+      <c r="B58" s="17" t="e" cm="1">
+        <f t="array" aca="1" ref="B58" ca="1">_xll.qlInstrumentNPV(B33,_xll.qlInstrumentSetPricingEngine(B33,$B$41,$B$52))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>94</v>
       </c>
-      <c r="B59" s="17" cm="1">
-        <f t="array" ref="B59">_xll.qlInstrumentNPV(B34,_xll.qlInstrumentSetPricingEngine(B34,$B$41,$B$52))</f>
-        <v>67.704758683644968</v>
+      <c r="B59" s="17" t="e" cm="1">
+        <f t="array" aca="1" ref="B59" ca="1">_xll.qlInstrumentNPV(B34,_xll.qlInstrumentSetPricingEngine(B34,$B$41,$B$52))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>27</v>
       </c>
-      <c r="B61" s="17" cm="1">
-        <f t="array" ref="B61">_xll.qlInstrumentNPV(B36,_xll.qlInstrumentSetPricingEngine(B36,$B$41,$B$52))</f>
-        <v>177.75574893499586</v>
+      <c r="B61" s="17" t="e" cm="1">
+        <f t="array" aca="1" ref="B61" ca="1">_xll.qlInstrumentNPV(B36,_xll.qlInstrumentSetPricingEngine(B36,$B$41,$B$52))</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>107</v>
       </c>
-      <c r="B62" s="17">
-        <f>B61-MAX(B55:B59)</f>
-        <v>54.144827827716924</v>
+      <c r="B62" s="17" t="e">
+        <f ca="1">B61-MAX(B55:B59)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/tests/workbooktests/workbooks/test_gaussian1dmodel.xlsx
+++ b/tests/workbooktests/workbooks/test_gaussian1dmodel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F786642-E4F7-4FE1-81CD-045F3DFD31B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{939C0DD8-CAD3-4101-B458-B3237FFFA754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{096EF196-26B4-4940-94D5-2518E57D2FCB}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{096EF196-26B4-4940-94D5-2518E57D2FCB}"/>
   </bookViews>
   <sheets>
     <sheet name="GSR Model and Engine" sheetId="1" r:id="rId1"/>
@@ -843,35 +843,35 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
+      <c r="B2" s="1" cm="1">
+        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="e" cm="1">
-        <f t="array" aca="1" ref="B4" ca="1">_xll.qlFlatForward(B2,0.03,"Act/365")</f>
-        <v>#VALUE!</v>
+      <c r="B4" t="str" cm="1">
+        <f t="array" ref="B4">_xll.qlFlatForward(B2,0.03,"Act/365")</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="1" t="e">
-        <f ca="1">B2+365</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="1" t="e">
-        <f ca="1">B8+365</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D8" s="1" t="e">
-        <f ca="1">C8+365</f>
-        <v>#VALUE!</v>
+      <c r="B8" s="1">
+        <f>B2+365</f>
+        <v>46539</v>
+      </c>
+      <c r="C8" s="1">
+        <f>B8+365</f>
+        <v>46904</v>
+      </c>
+      <c r="D8" s="1">
+        <f>C8+365</f>
+        <v>47269</v>
       </c>
       <c r="E8" s="1"/>
     </row>
@@ -921,36 +921,36 @@
       <c r="A13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B13" t="e" cm="1">
-        <f t="array" aca="1" ref="B13" ca="1">_xll.qlGsr(B4,B8:D8,B9:E9,B10:E10,B11)</f>
-        <v>#VALUE!</v>
+      <c r="B13" t="str" cm="1">
+        <f t="array" ref="B13">_xll.qlGsr(B4,B8:D8,B9:E9,B10:E10,B11)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R13C2Gsr,A</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B15" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlGaussian1dSwaptionEngine(B13)</f>
-        <v>#VALUE!</v>
+      <c r="B15" t="str" cm="1">
+        <f t="array" ref="B15">_xll.qlGaussian1dSwaptionEngine(B13)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R15C2Gaussian1dSwaptionEngine,A</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlFlatForward(B2,0.03)</f>
-        <v>#VALUE!</v>
+      <c r="B17" s="4" t="str" cm="1">
+        <f t="array" ref="B17">_xll.qlFlatForward(B2,0.03)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R17C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B18" ca="1">_xll.qlEuribor("6M",B17)</f>
-        <v>#VALUE!</v>
+      <c r="B18" s="4" t="str" cm="1">
+        <f t="array" ref="B18">_xll.qlEuribor("6M",B17)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -976,18 +976,18 @@
       <c r="A22" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B22" ca="1">_xll.qlCalendarAdvance2("Target",$B$2,B20,"ModifiedFollowing")</f>
-        <v>#VALUE!</v>
+      <c r="B22" s="3" cm="1">
+        <f t="array" ref="B22">_xll.qlCalendarAdvance("Target",$B$2,B20,"ModifiedFollowing")</f>
+        <v>46905</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="B23" ca="1">_xll.qlCalendarAdvance2("Target",$B$2,B21,"ModifiedFollowing")</f>
-        <v>#VALUE!</v>
+      <c r="B23" s="3" cm="1">
+        <f t="array" ref="B23">_xll.qlCalendarAdvance("Target",$B$2,B21,"ModifiedFollowing")</f>
+        <v>48001</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -1002,27 +1002,27 @@
       <c r="A25" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B25" ca="1">_xll.qlMakeSchedule(B22,B23,"1y",,"Target","ModifiedFollowing",,"Backward")</f>
-        <v>#VALUE!</v>
+      <c r="B25" s="4" t="str" cm="1">
+        <f t="array" ref="B25">_xll.qlMakeSchedule(B22,B23,"1y",,"Target","ModifiedFollowing",,"Backward")</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R25C2Schedule,A</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B26" ca="1">_xll.qlMakeSchedule(B22,B23,"6m",,"Target","ModifiedFollowing",,"Backward")</f>
-        <v>#VALUE!</v>
+      <c r="B26" s="4" t="str" cm="1">
+        <f t="array" ref="B26">_xll.qlMakeSchedule(B22,B23,"6m",,"Target","ModifiedFollowing",,"Backward")</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R26C2Schedule,A</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B27" ca="1">_xll.qlVanillaSwap("Payer",10000,B25,B24,"30/360",B26,B18,0,"Act/360")</f>
-        <v>#VALUE!</v>
+      <c r="B27" s="4" t="str" cm="1">
+        <f t="array" ref="B27">_xll.qlVanillaSwap("Payer",10000,B25,B24,"30/360",B26,B18,0,"Act/360")</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R27C2VanillaSwap,A</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -1032,22 +1032,30 @@
       <c r="A29" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B29" ca="1">_xll.qlScheduleDates(B25) - 2</f>
-        <v>#VALUE!</v>
+      <c r="B29" s="1" cm="1">
+        <f t="array" ref="B29:B33">_xll.qlScheduleDates(B25) - 2</f>
+        <v>46903</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B30" s="3"/>
+      <c r="B30" s="3">
+        <v>46904</v>
+      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B31" s="3"/>
+      <c r="B31" s="3">
+        <v>47271</v>
+      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B32" s="3"/>
+      <c r="B32" s="3">
+        <v>47635</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="6"/>
+      <c r="B33" s="6">
+        <v>47999</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B34" s="4"/>
@@ -1056,18 +1064,18 @@
       <c r="A35" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B35" ca="1">_xll.qlEuropeanExercise(B29)</f>
-        <v>#VALUE!</v>
+      <c r="B35" s="4" t="str" cm="1">
+        <f t="array" ref="B35">_xll.qlEuropeanExercise(B29)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R35C2EuropeanExercise,A</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B36" ca="1">_xll.qlBermudanExercise(B29:B32)</f>
-        <v>#VALUE!</v>
+      <c r="B36" s="4" t="str" cm="1">
+        <f t="array" ref="B36">_xll.qlBermudanExercise(B29:B32)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R36C2BermudanExercise,A</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1092,36 +1100,36 @@
       <c r="A41" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B41" ca="1">_xll.qlSwaption(B27,B35)</f>
-        <v>#VALUE!</v>
+      <c r="B41" s="4" t="str" cm="1">
+        <f t="array" ref="B41">_xll.qlSwaption(B27,B35)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R41C2Swaption,A</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>27</v>
       </c>
-      <c r="B42" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B42" ca="1">_xll.qlSwaption(B27,B36)</f>
-        <v>#VALUE!</v>
+      <c r="B42" s="4" t="str" cm="1">
+        <f t="array" ref="B42">_xll.qlSwaption(B27,B36)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R42C2Swaption,A</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>28</v>
       </c>
-      <c r="B44" t="e" cm="1">
-        <f t="array" aca="1" ref="B44" ca="1">_xll.qlInstrumentNPV(B41,_xll.qlInstrumentSetPricingEngine(B41,B15))</f>
-        <v>#VALUE!</v>
+      <c r="B44" cm="1">
+        <f t="array" ref="B44">_xll.qlInstrumentNPV(B41,_xll.qlInstrumentSetPricingEngine(B41,B15))</f>
+        <v>126.78027860072075</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>28</v>
       </c>
-      <c r="B45" t="e" cm="1">
-        <f t="array" aca="1" ref="B45" ca="1">_xll.qlInstrumentNPV(B42,_xll.qlInstrumentSetPricingEngine(B42,B15))</f>
-        <v>#VALUE!</v>
+      <c r="B45" cm="1">
+        <f t="array" ref="B45">_xll.qlInstrumentNPV(B42,_xll.qlInstrumentSetPricingEngine(B42,B15))</f>
+        <v>143.17547718731561</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1193,21 +1201,21 @@
       <c r="A52" t="s">
         <v>35</v>
       </c>
-      <c r="B52" s="4" t="e">
-        <f ca="1">$B$18</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C52" s="4" t="e">
-        <f ca="1">$B$18</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D52" s="4" t="e">
-        <f ca="1">$B$18</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E52" s="4" t="e">
-        <f ca="1">$B$18</f>
-        <v>#VALUE!</v>
+      <c r="B52" s="4" t="str">
+        <f>$B$18</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
+      </c>
+      <c r="C52" s="4" t="str">
+        <f>$B$18</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
+      </c>
+      <c r="D52" s="4" t="str">
+        <f>$B$18</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
+      </c>
+      <c r="E52" s="4" t="str">
+        <f>$B$18</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R18C2Euribor,A</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1265,21 +1273,21 @@
       <c r="A56" t="s">
         <v>42</v>
       </c>
-      <c r="B56" s="4" t="e">
-        <f ca="1">$B$4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C56" s="4" t="e">
-        <f ca="1">$B$4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D56" s="4" t="e">
-        <f ca="1">$B$4</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E56" s="4" t="e">
-        <f ca="1">$B$4</f>
-        <v>#VALUE!</v>
+      <c r="B56" s="4" t="str">
+        <f>$B$4</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="C56" s="4" t="str">
+        <f>$B$4</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="D56" s="4" t="str">
+        <f>$B$4</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
+      </c>
+      <c r="E56" s="4" t="str">
+        <f>$B$4</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R4C2YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1405,48 +1413,48 @@
       <c r="A65" t="s">
         <v>29</v>
       </c>
-      <c r="B65" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B65" ca="1">_xll.qlSwaptionHelper(B49,B50,B51,B52,B53,B54,B55,B56,B57,B58,B59,B60,B61,B62)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C65" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="C65" ca="1">_xll.qlSwaptionHelper(C49,C50,C51,C52,C53,C54,C55,C56,C57,C58,C59,C60,C61,C62)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D65" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="D65" ca="1">_xll.qlSwaptionHelper(D49,D50,D51,D52,D53,D54,D55,D56,D57,D58,D59,D60,D61,D62)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E65" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="E65" ca="1">_xll.qlSwaptionHelper(E49,E50,E51,E52,E53,E54,E55,E56,E57,E58,E59,E60,E61,E62)</f>
-        <v>#VALUE!</v>
+      <c r="B65" s="4" t="str" cm="1">
+        <f t="array" ref="B65">_xll.qlSwaptionHelper(B49,B50,B51,B52,B53,B54,B55,B56,B57,B58,B59,B60,B61,B62)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C2SwaptionHelper,A</v>
+      </c>
+      <c r="C65" s="4" t="str" cm="1">
+        <f t="array" ref="C65">_xll.qlSwaptionHelper(C49,C50,C51,C52,C53,C54,C55,C56,C57,C58,C59,C60,C61,C62)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C3SwaptionHelper,A</v>
+      </c>
+      <c r="D65" s="4" t="str" cm="1">
+        <f t="array" ref="D65">_xll.qlSwaptionHelper(D49,D50,D51,D52,D53,D54,D55,D56,D57,D58,D59,D60,D61,D62)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C4SwaptionHelper,A</v>
+      </c>
+      <c r="E65" s="4" t="str" cm="1">
+        <f t="array" ref="E65">_xll.qlSwaptionHelper(E49,E50,E51,E52,E53,E54,E55,E56,E57,E58,E59,E60,E61,E62)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R65C5SwaptionHelper,A</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B66" t="e" cm="1">
-        <f t="array" aca="1" ref="B66" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(B65,$B$15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C66" t="e" cm="1">
-        <f t="array" aca="1" ref="C66" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(C65,$B$15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D66" t="e" cm="1">
-        <f t="array" aca="1" ref="D66" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(D65,$B$15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E66" t="e" cm="1">
-        <f t="array" aca="1" ref="E66" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(E65,$B$15)</f>
-        <v>#VALUE!</v>
+      <c r="B66" t="b" cm="1">
+        <f t="array" ref="B66">_xll.qlBlackCalibrationHelperSetPricingEngine(B65,$B$15)</f>
+        <v>1</v>
+      </c>
+      <c r="C66" t="b" cm="1">
+        <f t="array" ref="C66">_xll.qlBlackCalibrationHelperSetPricingEngine(C65,$B$15)</f>
+        <v>1</v>
+      </c>
+      <c r="D66" t="b" cm="1">
+        <f t="array" ref="D66">_xll.qlBlackCalibrationHelperSetPricingEngine(D65,$B$15)</f>
+        <v>1</v>
+      </c>
+      <c r="E66" t="b" cm="1">
+        <f t="array" ref="E66">_xll.qlBlackCalibrationHelperSetPricingEngine(E65,$B$15)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>55</v>
       </c>
-      <c r="B68" t="e" cm="1">
-        <f t="array" aca="1" ref="B68" ca="1">_xll.qlLevenbergMarquardt(,,,,B66:E66)</f>
-        <v>#VALUE!</v>
+      <c r="B68" t="str" cm="1">
+        <f t="array" ref="B68">_xll.qlLevenbergMarquardt(,,,,B66:E66)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R68C2LevenbergMarquardt,A</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -1493,36 +1501,54 @@
       <c r="A75" t="s">
         <v>61</v>
       </c>
-      <c r="B75" t="e" cm="1">
-        <f t="array" aca="1" ref="B75" ca="1">_xll.qlEndCriteria(B70,B71,B72,B73,B74,B66:E66)</f>
-        <v>#VALUE!</v>
+      <c r="B75" t="str" cm="1">
+        <f t="array" ref="B75">_xll.qlEndCriteria(B70,B71,B72,B73,B74,B66:E66)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]GSR Model and Engine!R75C2EndCriteria,A</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>62</v>
       </c>
-      <c r="B77" t="e" cm="1">
-        <f t="array" aca="1" ref="B77" ca="1">_xll.qlGsrCalibrateVolatilitiesIterative(B13,B65:E65,B68,B75,,,B66:E66)</f>
-        <v>#VALUE!</v>
+      <c r="B77" t="b" cm="1">
+        <f t="array" ref="B77">_xll.qlGsrCalibrateVolatilitiesIterative(B13,B65:E65,B68,B75,,,B66:E66)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B79" t="e" cm="1">
-        <f t="array" aca="1" ref="B79" ca="1">TRANSPOSE(_xll.qlGsrVolatility(B13,B77))</f>
-        <v>#VALUE!</v>
+      <c r="B79" cm="1">
+        <f t="array" ref="B79:E79">TRANSPOSE(_xll.qlGsrVolatility(B13,B77))</f>
+        <v>6.9631874311834709E-3</v>
+      </c>
+      <c r="C79">
+        <v>6.9598377904623336E-3</v>
+      </c>
+      <c r="D79">
+        <v>6.9692472977815108E-3</v>
+      </c>
+      <c r="E79">
+        <v>6.999176212400815E-3</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B80" t="e" cm="1">
-        <f t="array" aca="1" ref="B80" ca="1">TRANSPOSE(_xll.qlGsrReversion(B13,B77))</f>
-        <v>#VALUE!</v>
+      <c r="B80" cm="1">
+        <f t="array" ref="B80:E80">TRANSPOSE(_xll.qlGsrReversion(B13,B77))</f>
+        <v>0.01</v>
+      </c>
+      <c r="C80">
+        <v>0.01</v>
+      </c>
+      <c r="D80">
+        <v>0.01</v>
+      </c>
+      <c r="E80">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -1562,9 +1588,9 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B2" ca="1">_xll.qlSettingsSetEvaluationDate(B1)</f>
-        <v>#VALUE!</v>
+      <c r="B2" s="1" cm="1">
+        <f t="array" ref="B2">_xll.qlSettingsSetEvaluationDate(B1)</f>
+        <v>46174</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
@@ -1654,33 +1680,33 @@
       <c r="J5" s="2">
         <v>6.7945145206867591E-3</v>
       </c>
-      <c r="K5" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="K5" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D5)</f>
-        <v>#VALUE!</v>
+      <c r="K5" s="1" cm="1">
+        <f t="array" ref="K5">_xll.qlCalendarAdvance($B$4,$B$2,D5)</f>
+        <v>46905</v>
       </c>
       <c r="L5" s="13"/>
       <c r="O5" s="12">
         <v>1</v>
       </c>
-      <c r="P5" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="P5" ca="1">INDEX(_xll.qlScheduleDates($B$20),O5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q5" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="Q5" ca="1">_xll.qlCalendarAdvance2($B$4,P5,"-2d")</f>
-        <v>#VALUE!</v>
+      <c r="P5" s="1" cm="1">
+        <f t="array" ref="P5">INDEX(_xll.qlScheduleDates($B$20),O5)</f>
+        <v>46541</v>
+      </c>
+      <c r="Q5" s="1" cm="1">
+        <f t="array" ref="Q5">_xll.qlCalendarAdvance($B$4,P5,"-2d")</f>
+        <v>46539</v>
       </c>
       <c r="R5" s="14" t="str">
         <f>(10-O5)&amp;"y"</f>
         <v>9y</v>
       </c>
-      <c r="S5" s="15" t="e" cm="1">
-        <f t="array" aca="1" ref="S5" ca="1">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q5,R5,$B$23)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T5" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="T5" ca="1">_xll.qlSwaptionHelper(Q5,R5,S5,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
-        <v>#VALUE!</v>
+      <c r="S5" s="15" cm="1">
+        <f t="array" ref="S5">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q5,R5,$B$23)</f>
+        <v>6.8416161029777513E-3</v>
+      </c>
+      <c r="T5" s="4" t="str" cm="1">
+        <f t="array" ref="T5">_xll.qlSwaptionHelper(Q5,R5,S5,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R5C20SwaptionHelper,A</v>
       </c>
       <c r="U5" s="13">
         <v>7.0000000000000001E-3</v>
@@ -1689,22 +1715,22 @@
         <f>$B$39</f>
         <v>0.03</v>
       </c>
-      <c r="W5" t="e" cm="1">
-        <f t="array" aca="1" ref="W5" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(T5,$B$41)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X5" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="X5" ca="1">_xll.qlGsrVolatility(B40,B52)</f>
-        <v>#VALUE!</v>
+      <c r="W5" t="b" cm="1">
+        <f t="array" ref="W5">_xll.qlBlackCalibrationHelperSetPricingEngine(T5,$B$41)</f>
+        <v>1</v>
+      </c>
+      <c r="X5" s="2" cm="1">
+        <f t="array" ref="X5:X10">_xll.qlGsrVolatility(B40,B52)</f>
+        <v>7.6211372531147341E-3</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B6" ca="1">_xll.qlFlatForward($B$2,0.03,"Act/365")</f>
-        <v>#VALUE!</v>
+      <c r="B6" s="4" t="str" cm="1">
+        <f t="array" ref="B6">_xll.qlFlatForward($B$2,0.03,"Act/365")</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R6C2YieldTermStructureHandle,A</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>68</v>
@@ -1727,32 +1753,32 @@
       <c r="J6" s="2">
         <v>6.7609933594352887E-3</v>
       </c>
-      <c r="K6" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="K6" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D6)</f>
-        <v>#VALUE!</v>
+      <c r="K6" s="1" cm="1">
+        <f t="array" ref="K6">_xll.qlCalendarAdvance($B$4,$B$2,D6)</f>
+        <v>47270</v>
       </c>
       <c r="O6" s="12">
         <v>3</v>
       </c>
-      <c r="P6" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="P6" ca="1">INDEX(_xll.qlScheduleDates($B$20),O6)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q6" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="Q6" ca="1">_xll.qlCalendarAdvance2($B$4,P6,"-2d")</f>
-        <v>#VALUE!</v>
+      <c r="P6" s="1" cm="1">
+        <f t="array" ref="P6">INDEX(_xll.qlScheduleDates($B$20),O6)</f>
+        <v>47273</v>
+      </c>
+      <c r="Q6" s="1" cm="1">
+        <f t="array" ref="Q6">_xll.qlCalendarAdvance($B$4,P6,"-2d")</f>
+        <v>47269</v>
       </c>
       <c r="R6" s="14" t="str">
         <f t="shared" ref="R6:R9" si="0">(10-O6)&amp;"y"</f>
         <v>7y</v>
       </c>
-      <c r="S6" s="15" t="e" cm="1">
-        <f t="array" aca="1" ref="S6" ca="1">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q6,R6,$B$23)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T6" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="T6" ca="1">_xll.qlSwaptionHelper(Q6,R6,S6,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
-        <v>#VALUE!</v>
+      <c r="S6" s="15" cm="1">
+        <f t="array" ref="S6">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q6,R6,$B$23)</f>
+        <v>6.8685932674608981E-3</v>
+      </c>
+      <c r="T6" s="4" t="str" cm="1">
+        <f t="array" ref="T6">_xll.qlSwaptionHelper(Q6,R6,S6,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R6C20SwaptionHelper,A</v>
       </c>
       <c r="U6" s="13">
         <v>7.0000000000000001E-3</v>
@@ -1761,19 +1787,21 @@
         <f t="shared" ref="V6:V10" si="1">$B$39</f>
         <v>0.03</v>
       </c>
-      <c r="W6" t="e" cm="1">
-        <f t="array" aca="1" ref="W6" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(T6,$B$41)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X6" s="2"/>
+      <c r="W6" t="b" cm="1">
+        <f t="array" ref="W6">_xll.qlBlackCalibrationHelperSetPricingEngine(T6,$B$41)</f>
+        <v>1</v>
+      </c>
+      <c r="X6" s="2">
+        <v>7.7086247092713412E-3</v>
+      </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B7" ca="1">_xll.qlFlatForward($B$2,0.02,"Act/365")</f>
-        <v>#VALUE!</v>
+      <c r="B7" s="4" t="str" cm="1">
+        <f t="array" ref="B7">_xll.qlFlatForward($B$2,0.02,"Act/365")</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R7C2YieldTermStructureHandle,A</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>69</v>
@@ -1796,32 +1824,32 @@
       <c r="J7" s="2">
         <v>6.667429100858718E-3</v>
       </c>
-      <c r="K7" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="K7" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D7)</f>
-        <v>#VALUE!</v>
+      <c r="K7" s="1" cm="1">
+        <f t="array" ref="K7">_xll.qlCalendarAdvance($B$4,$B$2,D7)</f>
+        <v>47637</v>
       </c>
       <c r="O7" s="12">
         <v>5</v>
       </c>
-      <c r="P7" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="P7" ca="1">INDEX(_xll.qlScheduleDates($B$20),O7)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q7" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="Q7" ca="1">_xll.qlCalendarAdvance2($B$4,P7,"-2d")</f>
-        <v>#VALUE!</v>
+      <c r="P7" s="1" cm="1">
+        <f t="array" ref="P7">INDEX(_xll.qlScheduleDates($B$20),O7)</f>
+        <v>48002</v>
+      </c>
+      <c r="Q7" s="1" cm="1">
+        <f t="array" ref="Q7">_xll.qlCalendarAdvance($B$4,P7,"-2d")</f>
+        <v>47998</v>
       </c>
       <c r="R7" s="14" t="str">
         <f t="shared" si="0"/>
         <v>5y</v>
       </c>
-      <c r="S7" s="15" t="e" cm="1">
-        <f t="array" aca="1" ref="S7" ca="1">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q7,R7,$B$23)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T7" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="T7" ca="1">_xll.qlSwaptionHelper(Q7,R7,S7,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
-        <v>#VALUE!</v>
+      <c r="S7" s="15" cm="1">
+        <f t="array" ref="S7">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q7,R7,$B$23)</f>
+        <v>6.8308101938307384E-3</v>
+      </c>
+      <c r="T7" s="4" t="str" cm="1">
+        <f t="array" ref="T7">_xll.qlSwaptionHelper(Q7,R7,S7,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R7C20SwaptionHelper,A</v>
       </c>
       <c r="U7" s="13">
         <v>7.0000000000000001E-3</v>
@@ -1830,11 +1858,13 @@
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="W7" t="e" cm="1">
-        <f t="array" aca="1" ref="W7" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(T7,$B$41)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X7" s="2"/>
+      <c r="W7" t="b" cm="1">
+        <f t="array" ref="W7">_xll.qlBlackCalibrationHelperSetPricingEngine(T7,$B$41)</f>
+        <v>1</v>
+      </c>
+      <c r="X7" s="2">
+        <v>7.5952162222981219E-3</v>
+      </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="D8" s="12" t="s">
@@ -1858,32 +1888,32 @@
       <c r="J8" s="2">
         <v>6.5734245883187388E-3</v>
       </c>
-      <c r="K8" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="K8" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D8)</f>
-        <v>#VALUE!</v>
+      <c r="K8" s="1" cm="1">
+        <f t="array" ref="K8">_xll.qlCalendarAdvance($B$4,$B$2,D8)</f>
+        <v>48001</v>
       </c>
       <c r="O8" s="12">
         <v>7</v>
       </c>
-      <c r="P8" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="P8" ca="1">INDEX(_xll.qlScheduleDates($B$20),O8)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q8" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="Q8" ca="1">_xll.qlCalendarAdvance2($B$4,P8,"-2d")</f>
-        <v>#VALUE!</v>
+      <c r="P8" s="1" cm="1">
+        <f t="array" ref="P8">INDEX(_xll.qlScheduleDates($B$20),O8)</f>
+        <v>48733</v>
+      </c>
+      <c r="Q8" s="1" cm="1">
+        <f t="array" ref="Q8">_xll.qlCalendarAdvance($B$4,P8,"-2d")</f>
+        <v>48731</v>
       </c>
       <c r="R8" s="14" t="str">
         <f t="shared" si="0"/>
         <v>3y</v>
       </c>
-      <c r="S8" s="15" t="e" cm="1">
-        <f t="array" aca="1" ref="S8" ca="1">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q8,R8,$B$23)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T8" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="T8" ca="1">_xll.qlSwaptionHelper(Q8,R8,S8,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
-        <v>#VALUE!</v>
+      <c r="S8" s="15" cm="1">
+        <f t="array" ref="S8">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q8,R8,$B$23)</f>
+        <v>6.7802047066821882E-3</v>
+      </c>
+      <c r="T8" s="4" t="str" cm="1">
+        <f t="array" ref="T8">_xll.qlSwaptionHelper(Q8,R8,S8,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R8C20SwaptionHelper,A</v>
       </c>
       <c r="U8" s="13">
         <v>7.0000000000000001E-3</v>
@@ -1892,19 +1922,21 @@
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="W8" t="e" cm="1">
-        <f t="array" aca="1" ref="W8" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(T8,$B$41)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X8" s="2"/>
+      <c r="W8" t="b" cm="1">
+        <f t="array" ref="W8">_xll.qlBlackCalibrationHelperSetPricingEngine(T8,$B$41)</f>
+        <v>1</v>
+      </c>
+      <c r="X8" s="2">
+        <v>7.4940275000536802E-3</v>
+      </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B9" ca="1">_xll.qlSwaptionVolatilityMatrix(B2,K5:K13,E4:J4,E5:J13,"act/365",,"Normal")</f>
-        <v>#VALUE!</v>
+      <c r="B9" s="4" t="str" cm="1">
+        <f t="array" ref="B9">_xll.qlSwaptionVolatilityMatrix(B2,K5:K13,E4:J4,E5:J13,"act/365",,"Normal")</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R9C2SwaptionVolatilityStructureHandle,A</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>70</v>
@@ -1927,32 +1959,32 @@
       <c r="J9" s="2">
         <v>6.4205016338086587E-3</v>
       </c>
-      <c r="K9" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="K9" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D9)</f>
-        <v>#VALUE!</v>
+      <c r="K9" s="1" cm="1">
+        <f t="array" ref="K9">_xll.qlCalendarAdvance($B$4,$B$2,D9)</f>
+        <v>48366</v>
       </c>
       <c r="O9" s="12">
         <v>9</v>
       </c>
-      <c r="P9" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="P9" ca="1">INDEX(_xll.qlScheduleDates($B$20),O9)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Q9" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="Q9" ca="1">_xll.qlCalendarAdvance2($B$4,P9,"-2d")</f>
-        <v>#VALUE!</v>
+      <c r="P9" s="1" cm="1">
+        <f t="array" ref="P9">INDEX(_xll.qlScheduleDates($B$20),O9)</f>
+        <v>49464</v>
+      </c>
+      <c r="Q9" s="1" cm="1">
+        <f t="array" ref="Q9">_xll.qlCalendarAdvance($B$4,P9,"-2d")</f>
+        <v>49460</v>
       </c>
       <c r="R9" s="14" t="str">
         <f t="shared" si="0"/>
         <v>1y</v>
       </c>
-      <c r="S9" s="15" t="e" cm="1">
-        <f t="array" aca="1" ref="S9" ca="1">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q9,R9,$B$23)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T9" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="T9" ca="1">_xll.qlSwaptionHelper(Q9,R9,S9,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
-        <v>#VALUE!</v>
+      <c r="S9" s="15" cm="1">
+        <f t="array" ref="S9">_xll.qlSwaptionVolatilityStructureVolatility($B$9,Q9,R9,$B$23)</f>
+        <v>6.7856340498962438E-3</v>
+      </c>
+      <c r="T9" s="4" t="str" cm="1">
+        <f t="array" ref="T9">_xll.qlSwaptionHelper(Q9,R9,S9,$B$11,"1y","30/360","act/360",$B$7,,$B$23,,"Normal",,2)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R9C20SwaptionHelper,A</v>
       </c>
       <c r="U9" s="13">
         <v>7.0000000000000001E-3</v>
@@ -1961,11 +1993,13 @@
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="W9" t="e" cm="1">
-        <f t="array" aca="1" ref="W9" ca="1">_xll.qlBlackCalibrationHelperSetPricingEngine(T9,$B$41)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X9" s="2"/>
+      <c r="W9" t="b" cm="1">
+        <f t="array" ref="W9">_xll.qlBlackCalibrationHelperSetPricingEngine(T9,$B$41)</f>
+        <v>1</v>
+      </c>
+      <c r="X9" s="2">
+        <v>7.5255128544236957E-3</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="D10" s="12" t="s">
@@ -1989,9 +2023,9 @@
       <c r="J10" s="2">
         <v>6.2645776071992877E-3</v>
       </c>
-      <c r="K10" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="K10" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D10)</f>
-        <v>#VALUE!</v>
+      <c r="K10" s="1" cm="1">
+        <f t="array" ref="K10">_xll.qlCalendarAdvance($B$4,$B$2,D10)</f>
+        <v>48731</v>
       </c>
       <c r="U10" s="13">
         <v>7.0000000000000001E-3</v>
@@ -2000,15 +2034,17 @@
         <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
-      <c r="X10" s="2"/>
+      <c r="X10" s="2">
+        <v>7.0000000000000001E-3</v>
+      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B11" ca="1">_xll.qlEuribor("6m",B6)</f>
-        <v>#VALUE!</v>
+      <c r="B11" s="4" t="str" cm="1">
+        <f t="array" ref="B11">_xll.qlEuribor("6m",B6)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R11C2Euribor,A</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>72</v>
@@ -2031,9 +2067,9 @@
       <c r="J11" s="2">
         <v>6.0960353967729093E-3</v>
       </c>
-      <c r="K11" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="K11" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D11)</f>
-        <v>#VALUE!</v>
+      <c r="K11" s="1" cm="1">
+        <f t="array" ref="K11">_xll.qlCalendarAdvance($B$4,$B$2,D11)</f>
+        <v>49096</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
@@ -2058,9 +2094,9 @@
       <c r="J12" s="2">
         <v>5.9343809605290482E-3</v>
       </c>
-      <c r="K12" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="K12" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D12)</f>
-        <v>#VALUE!</v>
+      <c r="K12" s="1" cm="1">
+        <f t="array" ref="K12">_xll.qlCalendarAdvance($B$4,$B$2,D12)</f>
+        <v>49461</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
@@ -2091,9 +2127,9 @@
       <c r="J13" s="2">
         <v>5.7827242854212382E-3</v>
       </c>
-      <c r="K13" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="K13" ca="1">_xll.qlCalendarAdvance2($B$4,$B$2,D13)</f>
-        <v>#VALUE!</v>
+      <c r="K13" s="1" cm="1">
+        <f t="array" ref="K13">_xll.qlCalendarAdvance($B$4,$B$2,D13)</f>
+        <v>49828</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
@@ -2116,9 +2152,9 @@
       <c r="A17" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlCalendarAdvance2($B$4,_xll.qlCalendarAdvance2($B$4,$B$2,$B$13),$B$15)</f>
-        <v>#VALUE!</v>
+      <c r="B17" s="1" cm="1">
+        <f t="array" ref="B17">_xll.qlCalendarAdvance($B$4,_xll.qlCalendarAdvance($B$4,$B$2,$B$13),$B$15)</f>
+        <v>46541</v>
       </c>
       <c r="L17" s="1"/>
     </row>
@@ -2126,9 +2162,9 @@
       <c r="A18" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B18" ca="1">_xll.qlCalendarAdvance2($B$4,$B$17,$B$14)</f>
-        <v>#VALUE!</v>
+      <c r="B18" s="1" cm="1">
+        <f t="array" ref="B18">_xll.qlCalendarAdvance($B$4,$B$17,$B$14)</f>
+        <v>50194</v>
       </c>
       <c r="L18" s="1"/>
     </row>
@@ -2139,9 +2175,9 @@
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B20" ca="1">_xll.qlMakeSchedule($B$17,$B$18,"1y",,$B$4,"Following",,"Backward")</f>
-        <v>#VALUE!</v>
+      <c r="B20" s="4" t="str" cm="1">
+        <f t="array" ref="B20">_xll.qlMakeSchedule($B$17,$B$18,"1y",,$B$4,"Following",,"Backward")</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R20C2Schedule,A</v>
       </c>
       <c r="L20" s="1"/>
     </row>
@@ -2149,9 +2185,9 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B21" ca="1">_xll.qlMakeSchedule($B$17,$B$18,"3m",,$B$4,"Following",,"Backward")</f>
-        <v>#VALUE!</v>
+      <c r="B21" s="4" t="str" cm="1">
+        <f t="array" ref="B21">_xll.qlMakeSchedule($B$17,$B$18,"3m",,$B$4,"Following",,"Backward")</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R21C2Schedule,A</v>
       </c>
       <c r="L21" s="1"/>
     </row>
@@ -2183,9 +2219,9 @@
       <c r="A26" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B26" ca="1">_xll.qlVanillaSwap("Payer",10000,$B$20,$B$23,$B$24,$B$21,$B$11,0,"act/360")</f>
-        <v>#VALUE!</v>
+      <c r="B26" s="4" t="str" cm="1">
+        <f t="array" ref="B26">_xll.qlVanillaSwap("Payer",10000,$B$20,$B$23,$B$24,$B$21,$B$11,0,"act/360")</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R26C2VanillaSwap,A</v>
       </c>
       <c r="L26" s="1"/>
     </row>
@@ -2196,63 +2232,63 @@
       <c r="A28" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B28" ca="1">_xll.qlBermudanExercise(Q5:Q9)</f>
-        <v>#VALUE!</v>
+      <c r="B28" s="4" t="str" cm="1">
+        <f t="array" ref="B28">_xll.qlBermudanExercise(Q5:Q9)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R28C2BermudanExercise,A</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>90</v>
       </c>
-      <c r="B30" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B30" ca="1">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q5))</f>
-        <v>#VALUE!</v>
+      <c r="B30" s="4" t="str" cm="1">
+        <f t="array" ref="B30">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q5))</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R30C2Swaption,A</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B31" ca="1">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q6))</f>
-        <v>#VALUE!</v>
+      <c r="B31" s="4" t="str" cm="1">
+        <f t="array" ref="B31">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q6))</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R31C2Swaption,A</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>92</v>
       </c>
-      <c r="B32" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B32" ca="1">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q7))</f>
-        <v>#VALUE!</v>
+      <c r="B32" s="4" t="str" cm="1">
+        <f t="array" ref="B32">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q7))</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R32C2Swaption,A</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B33" ca="1">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q8))</f>
-        <v>#VALUE!</v>
+      <c r="B33" s="4" t="str" cm="1">
+        <f t="array" ref="B33">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q8))</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R33C2Swaption,A</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B34" ca="1">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q9))</f>
-        <v>#VALUE!</v>
+      <c r="B34" s="4" t="str" cm="1">
+        <f t="array" ref="B34">_xll.qlSwaption($B$26,_xll.qlEuropeanExercise(Q9))</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R34C2Swaption,A</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B36" ca="1">_xll.qlSwaption(B26,B28)</f>
-        <v>#VALUE!</v>
+      <c r="B36" s="4" t="str" cm="1">
+        <f t="array" ref="B36">_xll.qlSwaption(B26,B28)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R36C2Swaption,A</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -2273,27 +2309,27 @@
       <c r="A40" t="s">
         <v>96</v>
       </c>
-      <c r="B40" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B40" ca="1">_xll.qlGsr(B7,Q5:Q9,U5:U10,V5:V10)</f>
-        <v>#VALUE!</v>
+      <c r="B40" s="4" t="str" cm="1">
+        <f t="array" ref="B40">_xll.qlGsr(B7,Q5:Q9,U5:U10,V5:V10)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R40C2Gsr,A</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B41" ca="1">_xll.qlGaussian1dSwaptionEngine(B40)</f>
-        <v>#VALUE!</v>
+      <c r="B41" s="4" t="str" cm="1">
+        <f t="array" ref="B41">_xll.qlGaussian1dSwaptionEngine(B40)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R41C2Gaussian1dSwaptionEngine,A</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B43" ca="1">_xll.qlLevenbergMarquardt(,,,,T5:T9)</f>
-        <v>#VALUE!</v>
+      <c r="B43" s="4" t="str" cm="1">
+        <f t="array" ref="B43">_xll.qlLevenbergMarquardt(,,,,T5:T9)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R43C2LevenbergMarquardt,A</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -2340,18 +2376,18 @@
       <c r="A50" t="s">
         <v>100</v>
       </c>
-      <c r="B50" s="4" t="e" cm="1">
-        <f t="array" aca="1" ref="B50" ca="1">_xll.qlEndCriteria(B45,B46,B47,B48,B49,T5:T9)</f>
-        <v>#VALUE!</v>
+      <c r="B50" s="4" t="str" cm="1">
+        <f t="array" ref="B50">_xll.qlEndCriteria(B45,B46,B47,B48,B49,T5:T9)</f>
+        <v>欣[test_gaussian1dmodel.xlsx]Bermudan Swaption!R50C2EndCriteria,A</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>105</v>
       </c>
-      <c r="B52" t="e" cm="1">
-        <f t="array" aca="1" ref="B52" ca="1">_xll.qlGsrCalibrateVolatilitiesIterative(B40,T5:T9,B43,B50,,,W5:W9)</f>
-        <v>#VALUE!</v>
+      <c r="B52" t="b" cm="1">
+        <f t="array" ref="B52">_xll.qlGsrCalibrateVolatilitiesIterative(B40,T5:T9,B43,B50,,,W5:W9)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -2363,63 +2399,63 @@
       <c r="A55" t="s">
         <v>90</v>
       </c>
-      <c r="B55" s="17" t="e" cm="1">
-        <f t="array" aca="1" ref="B55" ca="1">_xll.qlInstrumentNPV(B30,_xll.qlInstrumentSetPricingEngine(B30,$B$41,$B$52))</f>
-        <v>#VALUE!</v>
+      <c r="B55" s="17" cm="1">
+        <f t="array" ref="B55">_xll.qlInstrumentNPV(B30,_xll.qlInstrumentSetPricingEngine(B30,$B$41,$B$52))</f>
+        <v>21.703395415542996</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="17" t="e" cm="1">
-        <f t="array" aca="1" ref="B56" ca="1">_xll.qlInstrumentNPV(B31,_xll.qlInstrumentSetPricingEngine(B31,$B$41,$B$52))</f>
-        <v>#VALUE!</v>
+      <c r="B56" s="17" cm="1">
+        <f t="array" ref="B56">_xll.qlInstrumentNPV(B31,_xll.qlInstrumentSetPricingEngine(B31,$B$41,$B$52))</f>
+        <v>96.520281949826526</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>92</v>
       </c>
-      <c r="B57" s="17" t="e" cm="1">
-        <f t="array" aca="1" ref="B57" ca="1">_xll.qlInstrumentNPV(B32,_xll.qlInstrumentSetPricingEngine(B32,$B$41,$B$52))</f>
-        <v>#VALUE!</v>
+      <c r="B57" s="17" cm="1">
+        <f t="array" ref="B57">_xll.qlInstrumentNPV(B32,_xll.qlInstrumentSetPricingEngine(B32,$B$41,$B$52))</f>
+        <v>123.61092110729599</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>93</v>
       </c>
-      <c r="B58" s="17" t="e" cm="1">
-        <f t="array" aca="1" ref="B58" ca="1">_xll.qlInstrumentNPV(B33,_xll.qlInstrumentSetPricingEngine(B33,$B$41,$B$52))</f>
-        <v>#VALUE!</v>
+      <c r="B58" s="17" cm="1">
+        <f t="array" ref="B58">_xll.qlInstrumentNPV(B33,_xll.qlInstrumentSetPricingEngine(B33,$B$41,$B$52))</f>
+        <v>110.33999699797786</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>94</v>
       </c>
-      <c r="B59" s="17" t="e" cm="1">
-        <f t="array" aca="1" ref="B59" ca="1">_xll.qlInstrumentNPV(B34,_xll.qlInstrumentSetPricingEngine(B34,$B$41,$B$52))</f>
-        <v>#VALUE!</v>
+      <c r="B59" s="17" cm="1">
+        <f t="array" ref="B59">_xll.qlInstrumentNPV(B34,_xll.qlInstrumentSetPricingEngine(B34,$B$41,$B$52))</f>
+        <v>67.704758683639781</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>27</v>
       </c>
-      <c r="B61" s="17" t="e" cm="1">
-        <f t="array" aca="1" ref="B61" ca="1">_xll.qlInstrumentNPV(B36,_xll.qlInstrumentSetPricingEngine(B36,$B$41,$B$52))</f>
-        <v>#VALUE!</v>
+      <c r="B61" s="17" cm="1">
+        <f t="array" ref="B61">_xll.qlInstrumentNPV(B36,_xll.qlInstrumentSetPricingEngine(B36,$B$41,$B$52))</f>
+        <v>177.75574893498674</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>107</v>
       </c>
-      <c r="B62" s="17" t="e">
-        <f ca="1">B61-MAX(B55:B59)</f>
-        <v>#VALUE!</v>
+      <c r="B62" s="17">
+        <f>B61-MAX(B55:B59)</f>
+        <v>54.144827827690747</v>
       </c>
     </row>
   </sheetData>
